--- a/InvoiceLog.xlsx
+++ b/InvoiceLog.xlsx
@@ -1,78 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\crew\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349CDBAF-76EB-4C58-A824-EDD30F631118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>S.No</t>
-  </si>
-  <si>
-    <t>Filename</t>
-  </si>
-  <si>
-    <t>PostProcess</t>
-  </si>
-  <si>
-    <t>Line Items</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>Vendor Status</t>
-  </si>
-  <si>
-    <t>Vendor Name</t>
-  </si>
-  <si>
-    <t>Total Amount</t>
-  </si>
-  <si>
-    <t>Filename,UniqueID,UniqueID Type</t>
-  </si>
-  <si>
-    <t>Linecount</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -411,53 +420,449 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Filename</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PostProcess</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Line Items</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Vendor Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Filename,UniqueID,UniqueID Type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Linecount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2a4f4920-d291-401b-ae4b-94ca6784a8fc.json</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Al Pinner03172024-191457.json</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Al Pinner03172024-191623.json</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-163747.json</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-163816.json</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-163844.json</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-164144.json</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-164240.json</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-164308.json</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aleksandra Karkuszewska03182024-005403.json</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aleksandra Karkuszewska03182024-005623.json</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alessandro Natale03172024-183033.json</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2a4f4920-d291-401b-ae4b-94ca6784a8fc.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Al Pinner03172024-191457.pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Al Pinner03172024-191623.pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-163747.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-163816.pdf</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-163844.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-164144.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-164240.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alberto Grazioli03172024-164308.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aleksandra Karkuszewska03182024-005403.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Aleksandra Karkuszewska03182024-005623.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alessandro Natale03172024-183033.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
